--- a/demo-output/DEMO - Otter Client 2 (Update + Review)/AppointmentFlowSheet/DEMO - Otter Client 2 (Update + Review) Appointment Flow Sheet.xlsx
+++ b/demo-output/DEMO - Otter Client 2 (Update + Review)/AppointmentFlowSheet/DEMO - Otter Client 2 (Update + Review) Appointment Flow Sheet.xlsx
@@ -34,13 +34,13 @@
     <t xml:space="preserve">Virtual </t>
   </si>
   <si>
-    <t>July 12, 2026</t>
+    <t>July 30, 2026</t>
   </si>
   <si>
-    <t>BM:  not every day, soft</t>
+    <t xml:space="preserve">BM: </t>
   </si>
   <si>
-    <t>hormonal migraine; bloating; cramping; nausea; extreme cramping and nausea after dinner; bladder issues; low energy; TMJ; armpit issues</t>
+    <t>the gallbladder pain is back; hormonal migraine; bloating cramping; bladder issues; extreme cramping and nausea after dinner</t>
   </si>
   <si>
     <t xml:space="preserve">LAYING 1 FOUNDATIONS:
@@ -54,10 +54,8 @@
 CNS:
 DENTAL: 
 HORMONAL: 
-ADDITIONAL:
-liver issues
-hormonal imbalance
-fungus in the small intestines
+ADDITIONAL: fungus is showing up for the small intestines
+hormonally good
 sluggish bile</t>
   </si>
   <si>
@@ -262,236 +260,241 @@
     </r>
   </si>
   <si>
-    <t>Start Pro Symbiotic</t>
+    <t xml:space="preserve">Continue GI Adsorb
+Start Pro Symbiotic
+Stop Smart Metal
+Stop Sam E
+Continue B12
+Start Psyllium</t>
   </si>
   <si>
-    <t>SLEEP:</t>
+    <t>SLEEP: mornings is like flipped. I don't have an afternoon crash</t>
   </si>
   <si>
     <t>WATER:</t>
   </si>
   <si>
-    <t>CYCLE: long periods, 7-8 days</t>
+    <t>CYCLE: I got my period on Sunday</t>
   </si>
   <si>
-    <t>EXERCISE: hard to work out in the mornings</t>
+    <t>EXERCISE: I have a really hard time working out in the mornings</t>
   </si>
   <si>
     <t>DIET:</t>
   </si>
   <si>
-    <t xml:space="preserve">BM: </t>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>LAYING 1 FOUNDATIONS</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>STANDING FOUNDATIONS</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+HTA</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+HTA POST RUN</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+LAYING 2 FOUNDATIONS</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ART</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+OPEN</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 
+SWITCH</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 
+CNS</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+DENTAL</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+HORMONAL</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 
+ADDITIONAL</t>
+    </r>
+    <r>
+      <rPr>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:</t>
+    </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>LAYING 1 FOUNDATIONS</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>STANDING FOUNDATIONS</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-HTA</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-HTA POST RUN</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-LAYING 2 FOUNDATIONS</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>ART</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-OPEN</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> 
-SWITCH</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> 
-CNS</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-DENTAL</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">
-HORMONAL</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve"> 
-ADDITIONAL</t>
-    </r>
-    <r>
-      <rPr>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>:</t>
-    </r>
+    <t>SLEEP:</t>
   </si>
   <si>
     <t>CYCLE:</t>
@@ -1330,11 +1333,11 @@
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
       <c r="B15" s="9" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>11</v>
@@ -1384,7 +1387,7 @@
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="15"/>
       <c r="B17" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -1672,11 +1675,11 @@
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
       <c r="B28" s="9" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>11</v>
@@ -1726,7 +1729,7 @@
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="15"/>
       <c r="B30" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -2014,11 +2017,11 @@
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
       <c r="B41" s="9" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>11</v>
@@ -2068,7 +2071,7 @@
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -2356,11 +2359,11 @@
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
       <c r="B54" s="9" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>11</v>
@@ -2410,7 +2413,7 @@
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="15"/>
       <c r="B56" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
@@ -2698,11 +2701,11 @@
     <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" s="8"/>
       <c r="B67" s="9" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>11</v>
@@ -2752,7 +2755,7 @@
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" s="15"/>
       <c r="B69" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
@@ -3040,11 +3043,11 @@
     <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" s="8"/>
       <c r="B80" s="9" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>11</v>
@@ -3094,7 +3097,7 @@
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" s="15"/>
       <c r="B82" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C82" s="17"/>
       <c r="D82" s="17"/>
